--- a/inasistencias-7b/alumnos-7b.xlsx
+++ b/inasistencias-7b/alumnos-7b.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2306" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2309" uniqueCount="419">
   <si>
     <t xml:space="preserve">total</t>
   </si>
@@ -328,6 +328,15 @@
   </si>
   <si>
     <t xml:space="preserve">Asis+posi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diciembre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x</t>
   </si>
   <si>
     <t xml:space="preserve">Torrez (cola pinto)</t>
@@ -1315,7 +1324,7 @@
       <family val="0"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1332,6 +1341,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFA726"/>
         <bgColor rgb="FFFFCC00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF4000"/>
+        <bgColor rgb="FFCC0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -1376,7 +1391,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1401,6 +1416,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1417,7 +1436,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1598,7 +1633,7 @@
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFFA726"/>
-      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FFFF4000"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
@@ -1725,7 +1760,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AO27"/>
+  <dimension ref="A1:AP27"/>
   <sheetFormatPr defaultColWidth="8.76953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.43"/>
@@ -1739,6 +1774,7 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="19" min="15" style="1" width="8.69"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="35" min="20" style="1" width="8.77"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="37" min="36" style="2" width="8.77"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="41" min="38" style="0" width="8.77"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1884,8 +1920,11 @@
       <c r="AO2" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AP2" s="6" t="n">
+        <v>45995</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
@@ -1938,14 +1977,14 @@
         <f aca="false">O3+P3/2+Q3/4</f>
         <v>8</v>
       </c>
-      <c r="S3" s="6" t="n">
+      <c r="S3" s="7" t="n">
         <f aca="false">ROUND(R3*10/$U$1,0)</f>
         <v>10</v>
       </c>
       <c r="T3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="U3" s="7" t="n">
+      <c r="U3" s="8" t="n">
         <v>0.652777777777778</v>
       </c>
       <c r="V3" s="1" t="s">
@@ -1972,7 +2011,7 @@
       <c r="AF3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AG3" s="7" t="n">
+      <c r="AG3" s="8" t="n">
         <v>0.666666666666667</v>
       </c>
       <c r="AH3" s="3" t="s">
@@ -1996,12 +2035,12 @@
         <f aca="false">COUNTIF(T3:AH3,"T")</f>
         <v>1</v>
       </c>
-      <c r="AO3" s="8" t="n">
+      <c r="AO3" s="9" t="n">
         <f aca="false">ROUND(AL3+AM3/2+AN3/4,0)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
@@ -2054,7 +2093,7 @@
         <f aca="false">O4+P4/2+Q4/4</f>
         <v>8</v>
       </c>
-      <c r="S4" s="6" t="n">
+      <c r="S4" s="7" t="n">
         <f aca="false">ROUND(R4*10/$U$1,0)</f>
         <v>10</v>
       </c>
@@ -2106,12 +2145,12 @@
         <f aca="false">COUNTIF(T4:AH4,"T")</f>
         <v>0</v>
       </c>
-      <c r="AO4" s="8" t="n">
+      <c r="AO4" s="9" t="n">
         <f aca="false">ROUND(AL4+AM4/2+AN4/4,0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
@@ -2164,7 +2203,7 @@
         <f aca="false">O5+P5/2+Q5/4</f>
         <v>7</v>
       </c>
-      <c r="S5" s="6" t="n">
+      <c r="S5" s="7" t="n">
         <f aca="false">ROUND(R5*10/$U$1,0)</f>
         <v>9</v>
       </c>
@@ -2216,12 +2255,12 @@
         <f aca="false">COUNTIF(T5:AH5,"T")</f>
         <v>0</v>
       </c>
-      <c r="AO5" s="8" t="n">
+      <c r="AO5" s="9" t="n">
         <f aca="false">ROUND(AL5+AM5/2+AN5/4,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
@@ -2274,7 +2313,7 @@
         <f aca="false">O6+P6/2+Q6/4</f>
         <v>6</v>
       </c>
-      <c r="S6" s="6" t="n">
+      <c r="S6" s="7" t="n">
         <f aca="false">ROUND(R6*10/$U$1,0)</f>
         <v>8</v>
       </c>
@@ -2326,12 +2365,12 @@
         <f aca="false">COUNTIF(T6:AH6,"T")</f>
         <v>0</v>
       </c>
-      <c r="AO6" s="8" t="n">
+      <c r="AO6" s="9" t="n">
         <f aca="false">ROUND(AL6+AM6/2+AN6/4,0)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
@@ -2384,7 +2423,7 @@
         <f aca="false">O7+P7/2+Q7/4</f>
         <v>8</v>
       </c>
-      <c r="S7" s="6" t="n">
+      <c r="S7" s="7" t="n">
         <f aca="false">ROUND(R7*10/$U$1,0)</f>
         <v>10</v>
       </c>
@@ -2406,7 +2445,7 @@
       <c r="AA7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AB7" s="7" t="n">
+      <c r="AB7" s="8" t="n">
         <v>0.645833333333333</v>
       </c>
       <c r="AC7" s="3" t="s">
@@ -2439,7 +2478,7 @@
         <f aca="false">COUNTIF(T7:AH7,"T")</f>
         <v>0</v>
       </c>
-      <c r="AO7" s="8" t="n">
+      <c r="AO7" s="9" t="n">
         <f aca="false">ROUND(AL7+AM7/2+AN7/4,0)</f>
         <v>8</v>
       </c>
@@ -2466,7 +2505,7 @@
       <c r="G8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="H8" s="8" t="n">
         <v>0.680555555555555</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -2500,7 +2539,7 @@
         <f aca="false">O8+P8/2+Q8/4</f>
         <v>2.25</v>
       </c>
-      <c r="S8" s="6" t="n">
+      <c r="S8" s="7" t="n">
         <f aca="false">ROUND(R8*10/$U$1,0)</f>
         <v>3</v>
       </c>
@@ -2552,12 +2591,12 @@
         <f aca="false">COUNTIF(T8:AH8,"T")</f>
         <v>0</v>
       </c>
-      <c r="AO8" s="8" t="n">
+      <c r="AO8" s="9" t="n">
         <f aca="false">ROUND(AL8+AM8/2+AN8/4,0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
@@ -2582,7 +2621,7 @@
       <c r="I9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="7" t="n">
+      <c r="J9" s="8" t="n">
         <v>0.618055555555556</v>
       </c>
       <c r="K9" s="1" t="s">
@@ -2613,7 +2652,7 @@
         <f aca="false">O9+P9/2+Q9/4</f>
         <v>7.5</v>
       </c>
-      <c r="S9" s="6" t="n">
+      <c r="S9" s="7" t="n">
         <f aca="false">ROUND(R9*10/$U$1,0)</f>
         <v>9</v>
       </c>
@@ -2626,7 +2665,7 @@
       <c r="W9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="X9" s="7" t="n">
+      <c r="X9" s="8" t="n">
         <v>0.645833333333333</v>
       </c>
       <c r="Y9" s="1" t="s">
@@ -2644,7 +2683,7 @@
       <c r="AD9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AE9" s="7" t="n">
+      <c r="AE9" s="8" t="n">
         <v>0.6875</v>
       </c>
       <c r="AF9" s="3" t="s">
@@ -2653,7 +2692,7 @@
       <c r="AH9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AI9" s="7" t="n">
+      <c r="AI9" s="8" t="n">
         <v>0.666666666666667</v>
       </c>
       <c r="AJ9" s="2" t="s">
@@ -2674,12 +2713,12 @@
         <f aca="false">COUNTIF(T9:AH9,"T")</f>
         <v>2</v>
       </c>
-      <c r="AO9" s="8" t="n">
+      <c r="AO9" s="9" t="n">
         <f aca="false">ROUND(AL9+AM9/2+AN9/4,0)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
@@ -2732,7 +2771,7 @@
         <f aca="false">O10+P10/2+Q10/4</f>
         <v>8</v>
       </c>
-      <c r="S10" s="6" t="n">
+      <c r="S10" s="7" t="n">
         <f aca="false">ROUND(R10*10/$U$1,0)</f>
         <v>10</v>
       </c>
@@ -2784,12 +2823,12 @@
         <f aca="false">COUNTIF(T10:AH10,"T")</f>
         <v>0</v>
       </c>
-      <c r="AO10" s="8" t="n">
+      <c r="AO10" s="9" t="n">
         <f aca="false">ROUND(AL10+AM10/2+AN10/4,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
@@ -2842,7 +2881,7 @@
         <f aca="false">O11+P11/2+Q11/4</f>
         <v>8</v>
       </c>
-      <c r="S11" s="6" t="n">
+      <c r="S11" s="7" t="n">
         <f aca="false">ROUND(R11*10/$U$1,0)</f>
         <v>10</v>
       </c>
@@ -2894,12 +2933,12 @@
         <f aca="false">COUNTIF(T11:AH11,"T")</f>
         <v>0</v>
       </c>
-      <c r="AO11" s="8" t="n">
+      <c r="AO11" s="9" t="n">
         <f aca="false">ROUND(AL11+AM11/2+AN11/4,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
@@ -2952,7 +2991,7 @@
         <f aca="false">O12+P12/2+Q12/4</f>
         <v>7</v>
       </c>
-      <c r="S12" s="6" t="n">
+      <c r="S12" s="7" t="n">
         <f aca="false">ROUND(R12*10/$U$1,0)</f>
         <v>9</v>
       </c>
@@ -3004,12 +3043,12 @@
         <f aca="false">COUNTIF(T12:AH12,"T")</f>
         <v>0</v>
       </c>
-      <c r="AO12" s="8" t="n">
+      <c r="AO12" s="9" t="n">
         <f aca="false">ROUND(AL12+AM12/2+AN12/4,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
@@ -3062,7 +3101,7 @@
         <f aca="false">O13+P13/2+Q13/4</f>
         <v>8</v>
       </c>
-      <c r="S13" s="6" t="n">
+      <c r="S13" s="7" t="n">
         <f aca="false">ROUND(R13*10/$U$1,0)</f>
         <v>10</v>
       </c>
@@ -3075,13 +3114,13 @@
       <c r="W13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="X13" s="7" t="n">
+      <c r="X13" s="8" t="n">
         <v>0.666666666666667</v>
       </c>
       <c r="Y13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Z13" s="9" t="s">
+      <c r="Z13" s="10" t="s">
         <v>48</v>
       </c>
       <c r="AA13" s="1" t="s">
@@ -3093,7 +3132,7 @@
       <c r="AD13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AE13" s="7" t="n">
+      <c r="AE13" s="8" t="n">
         <v>0.659722222222222</v>
       </c>
       <c r="AF13" s="3" t="s">
@@ -3120,12 +3159,12 @@
         <f aca="false">COUNTIF(T13:AH13,"T")</f>
         <v>1</v>
       </c>
-      <c r="AO13" s="8" t="n">
+      <c r="AO13" s="9" t="n">
         <f aca="false">ROUND(AL13+AM13/2+AN13/4,0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
@@ -3178,7 +3217,7 @@
         <f aca="false">O14+P14/2+Q14/4</f>
         <v>8</v>
       </c>
-      <c r="S14" s="6" t="n">
+      <c r="S14" s="7" t="n">
         <f aca="false">ROUND(R14*10/$U$1,0)</f>
         <v>10</v>
       </c>
@@ -3230,12 +3269,12 @@
         <f aca="false">COUNTIF(T14:AH14,"T")</f>
         <v>0</v>
       </c>
-      <c r="AO14" s="8" t="n">
+      <c r="AO14" s="9" t="n">
         <f aca="false">ROUND(AL14+AM14/2+AN14/4,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
@@ -3257,7 +3296,7 @@
       <c r="G15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H15" s="7" t="n">
+      <c r="H15" s="8" t="n">
         <v>0.666666666666667</v>
       </c>
       <c r="I15" s="1" t="s">
@@ -3291,7 +3330,7 @@
         <f aca="false">O15+P15/2+Q15/4</f>
         <v>6.75</v>
       </c>
-      <c r="S15" s="6" t="n">
+      <c r="S15" s="7" t="n">
         <f aca="false">ROUND(R15*10/$U$1,0)</f>
         <v>8</v>
       </c>
@@ -3343,12 +3382,12 @@
         <f aca="false">COUNTIF(T15:AH15,"T")</f>
         <v>0</v>
       </c>
-      <c r="AO15" s="8" t="n">
+      <c r="AO15" s="9" t="n">
         <f aca="false">ROUND(AL15+AM15/2+AN15/4,0)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
@@ -3401,14 +3440,14 @@
         <f aca="false">O16+P16/2+Q16/4</f>
         <v>8</v>
       </c>
-      <c r="S16" s="6" t="n">
+      <c r="S16" s="7" t="n">
         <f aca="false">ROUND(R16*10/$U$1,0)</f>
         <v>10</v>
       </c>
       <c r="T16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="U16" s="7" t="n">
+      <c r="U16" s="8" t="n">
         <v>0.652777777777778</v>
       </c>
       <c r="V16" s="1" t="s">
@@ -3456,12 +3495,12 @@
         <f aca="false">COUNTIF(T16:AH16,"T")</f>
         <v>0</v>
       </c>
-      <c r="AO16" s="8" t="n">
+      <c r="AO16" s="9" t="n">
         <f aca="false">ROUND(AL16+AM16/2+AN16/4,0)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
@@ -3514,7 +3553,7 @@
         <f aca="false">O17+P17/2+Q17/4</f>
         <v>7</v>
       </c>
-      <c r="S17" s="6" t="n">
+      <c r="S17" s="7" t="n">
         <f aca="false">ROUND(R17*10/$U$1,0)</f>
         <v>9</v>
       </c>
@@ -3527,7 +3566,7 @@
       <c r="W17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="X17" s="7" t="n">
+      <c r="X17" s="8" t="n">
         <v>0.666666666666667</v>
       </c>
       <c r="Y17" s="1" t="s">
@@ -3545,7 +3584,7 @@
       <c r="AD17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="AE17" s="7" t="n">
+      <c r="AE17" s="8" t="n">
         <v>0.625</v>
       </c>
       <c r="AF17" s="3" t="s">
@@ -3572,12 +3611,12 @@
         <f aca="false">COUNTIF(T17:AH17,"T")</f>
         <v>0</v>
       </c>
-      <c r="AO17" s="8" t="n">
+      <c r="AO17" s="9" t="n">
         <f aca="false">ROUND(AL17+AM17/2+AN17/4,0)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
@@ -3630,7 +3669,7 @@
         <f aca="false">O18+P18/2+Q18/4</f>
         <v>5</v>
       </c>
-      <c r="S18" s="6" t="n">
+      <c r="S18" s="7" t="n">
         <f aca="false">ROUND(R18*10/$U$1,0)</f>
         <v>6</v>
       </c>
@@ -3643,7 +3682,7 @@
       <c r="W18" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="X18" s="7" t="n">
+      <c r="X18" s="8" t="n">
         <v>0.666666666666667</v>
       </c>
       <c r="Y18" s="1" t="s">
@@ -3664,7 +3703,7 @@
       <c r="AF18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AG18" s="7" t="n">
+      <c r="AG18" s="8" t="n">
         <v>0.666666666666667</v>
       </c>
       <c r="AH18" s="3" t="s">
@@ -3688,12 +3727,12 @@
         <f aca="false">COUNTIF(T18:AH18,"T")</f>
         <v>1</v>
       </c>
-      <c r="AO18" s="8" t="n">
+      <c r="AO18" s="9" t="n">
         <f aca="false">ROUND(AL18+AM18/2+AN18/4,0)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
@@ -3746,7 +3785,7 @@
         <f aca="false">O19+P19/2+Q19/4</f>
         <v>8</v>
       </c>
-      <c r="S19" s="6" t="n">
+      <c r="S19" s="7" t="n">
         <f aca="false">ROUND(R19*10/$U$1,0)</f>
         <v>10</v>
       </c>
@@ -3798,7 +3837,7 @@
         <f aca="false">COUNTIF(T19:AH19,"T")</f>
         <v>0</v>
       </c>
-      <c r="AO19" s="8" t="n">
+      <c r="AO19" s="9" t="n">
         <f aca="false">ROUND(AL19+AM19/2+AN19/4,0)</f>
         <v>10</v>
       </c>
@@ -3825,7 +3864,7 @@
       <c r="G20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="7" t="n">
+      <c r="H20" s="8" t="n">
         <v>0.652777777777778</v>
       </c>
       <c r="I20" s="1" t="s">
@@ -3859,7 +3898,7 @@
         <f aca="false">O20+P20/2+Q20/4</f>
         <v>6.5</v>
       </c>
-      <c r="S20" s="6" t="n">
+      <c r="S20" s="7" t="n">
         <f aca="false">ROUND(R20*10/$U$1,0)</f>
         <v>8</v>
       </c>
@@ -3911,12 +3950,12 @@
         <f aca="false">COUNTIF(T20:AH20,"T")</f>
         <v>0</v>
       </c>
-      <c r="AO20" s="8" t="n">
+      <c r="AO20" s="9" t="n">
         <f aca="false">ROUND(AL20+AM20/2+AN20/4,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
@@ -3969,7 +4008,7 @@
         <f aca="false">O21+P21/2+Q21/4</f>
         <v>6</v>
       </c>
-      <c r="S21" s="6" t="n">
+      <c r="S21" s="7" t="n">
         <f aca="false">ROUND(R21*10/$U$1,0)</f>
         <v>8</v>
       </c>
@@ -4021,7 +4060,7 @@
         <f aca="false">COUNTIF(T21:AH21,"T")</f>
         <v>0</v>
       </c>
-      <c r="AO21" s="8" t="n">
+      <c r="AO21" s="9" t="n">
         <f aca="false">ROUND(AL21+AM21/2+AN21/4,0)</f>
         <v>9</v>
       </c>
@@ -4079,7 +4118,7 @@
         <f aca="false">O22+P22/2+Q22/4</f>
         <v>2</v>
       </c>
-      <c r="S22" s="6" t="n">
+      <c r="S22" s="7" t="n">
         <f aca="false">ROUND(R22*10/$U$1,0)</f>
         <v>3</v>
       </c>
@@ -4131,12 +4170,12 @@
         <f aca="false">COUNTIF(T22:AH22,"T")</f>
         <v>0</v>
       </c>
-      <c r="AO22" s="8" t="n">
+      <c r="AO22" s="9" t="n">
         <f aca="false">ROUND(AL22+AM22/2+AN22/4,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
@@ -4189,14 +4228,14 @@
         <f aca="false">O23+P23/2+Q23/4</f>
         <v>8</v>
       </c>
-      <c r="S23" s="6" t="n">
+      <c r="S23" s="7" t="n">
         <f aca="false">ROUND(R23*10/$U$1,0)</f>
         <v>10</v>
       </c>
       <c r="T23" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="U23" s="7" t="n">
+      <c r="U23" s="8" t="n">
         <v>0.652777777777778</v>
       </c>
       <c r="V23" s="1" t="s">
@@ -4244,7 +4283,7 @@
         <f aca="false">COUNTIF(T23:AH23,"T")</f>
         <v>0</v>
       </c>
-      <c r="AO23" s="8" t="n">
+      <c r="AO23" s="9" t="n">
         <f aca="false">ROUND(AL23+AM23/2+AN23/4,0)</f>
         <v>6</v>
       </c>
@@ -4328,11 +4367,11 @@
         <f aca="false">COUNTIF(AH3:AH23,"P")</f>
         <v>16</v>
       </c>
-      <c r="AJ24" s="9" t="n">
+      <c r="AJ24" s="10" t="n">
         <f aca="false">COUNTIF(AJ3:AJ23,"P")</f>
         <v>9</v>
       </c>
-      <c r="AK24" s="9" t="n">
+      <c r="AK24" s="10" t="n">
         <f aca="false">COUNTIF(AK3:AK23,"P")</f>
         <v>7</v>
       </c>
@@ -4384,11 +4423,11 @@
         <f aca="false">COUNTIF(AH3:AH23,"M")</f>
         <v>0</v>
       </c>
-      <c r="AJ25" s="9" t="n">
+      <c r="AJ25" s="10" t="n">
         <f aca="false">COUNTIF(AJ3:AJ23,"M")</f>
         <v>0</v>
       </c>
-      <c r="AK25" s="9" t="n">
+      <c r="AK25" s="10" t="n">
         <f aca="false">COUNTIF(AK3:AK23,"M")</f>
         <v>0</v>
       </c>
@@ -4437,11 +4476,11 @@
         <f aca="false">COUNTIF(AH3:AH23,"T")</f>
         <v>1</v>
       </c>
-      <c r="AJ26" s="9" t="n">
+      <c r="AJ26" s="10" t="n">
         <f aca="false">COUNTIF(AJ3:AJ23,"T")</f>
         <v>0</v>
       </c>
-      <c r="AK26" s="9" t="n">
+      <c r="AK26" s="10" t="n">
         <f aca="false">COUNTIF(AK3:AK23,"T")</f>
         <v>0</v>
       </c>
@@ -4490,11 +4529,11 @@
         <f aca="false">SUM(AH24:AH26)</f>
         <v>17</v>
       </c>
-      <c r="AJ27" s="9" t="n">
+      <c r="AJ27" s="10" t="n">
         <f aca="false">SUM(AJ24:AJ26)</f>
         <v>9</v>
       </c>
-      <c r="AK27" s="9" t="n">
+      <c r="AK27" s="10" t="n">
         <f aca="false">SUM(AK24:AK26)</f>
         <v>7</v>
       </c>
@@ -4542,22 +4581,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>94</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4599,10 +4638,10 @@
         <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>9</v>
@@ -4624,10 +4663,10 @@
         <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>7</v>
@@ -4638,10 +4677,10 @@
         <v>22</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>5</v>
@@ -4658,10 +4697,10 @@
         <v>25</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>9</v>
@@ -4681,10 +4720,10 @@
         <v>28</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>7</v>
@@ -4732,10 +4771,10 @@
         <v>37</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>10</v>
@@ -4757,10 +4796,10 @@
         <v>37</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>6</v>
@@ -4771,10 +4810,10 @@
         <v>37</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>5</v>
@@ -4785,10 +4824,10 @@
         <v>37</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>3</v>
@@ -4819,10 +4858,10 @@
         <v>43</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>10</v>
@@ -4844,10 +4883,10 @@
         <v>43</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>5</v>
@@ -4878,10 +4917,10 @@
         <v>50</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>7</v>
@@ -4901,10 +4940,10 @@
         <v>53</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>10</v>
@@ -4924,10 +4963,10 @@
         <v>56</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>10</v>
@@ -4949,10 +4988,10 @@
         <v>56</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>7</v>
@@ -4969,10 +5008,10 @@
         <v>59</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>9</v>
@@ -4992,10 +5031,10 @@
         <v>62</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>10</v>
@@ -5015,10 +5054,10 @@
         <v>65</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -5038,10 +5077,10 @@
         <v>68</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -5061,10 +5100,10 @@
         <v>71</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>9</v>
@@ -5086,10 +5125,10 @@
         <v>71</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>5</v>
@@ -5100,7 +5139,7 @@
         <v>20</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>1</v>
@@ -5120,10 +5159,10 @@
         <v>74</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>8</v>
@@ -5145,10 +5184,10 @@
         <v>74</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>6</v>
@@ -5165,10 +5204,10 @@
         <v>76</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>10</v>
@@ -5190,10 +5229,10 @@
         <v>76</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>3</v>
@@ -5242,19 +5281,19 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>94</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5285,7 +5324,7 @@
         <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>9</v>
@@ -5298,7 +5337,7 @@
       <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -5308,7 +5347,7 @@
         <v>21</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>9</v>
@@ -5333,7 +5372,7 @@
         <v>21</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>7</v>
@@ -5347,7 +5386,7 @@
         <v>21</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>5</v>
@@ -5367,7 +5406,7 @@
         <v>24</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>9</v>
@@ -5390,7 +5429,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>7</v>
@@ -5413,7 +5452,7 @@
         <v>30</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>10</v>
@@ -5440,7 +5479,7 @@
       <c r="A11" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="10" t="s">
         <v>37</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -5450,7 +5489,7 @@
         <v>36</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>10</v>
@@ -5475,7 +5514,7 @@
         <v>36</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>10</v>
@@ -5489,7 +5528,7 @@
         <v>36</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>9</v>
@@ -5503,7 +5542,7 @@
         <v>36</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>8</v>
@@ -5517,7 +5556,7 @@
         <v>36</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>8</v>
@@ -5531,7 +5570,7 @@
         <v>36</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>6</v>
@@ -5545,7 +5584,7 @@
         <v>36</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>5</v>
@@ -5559,7 +5598,7 @@
         <v>36</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>3</v>
@@ -5593,7 +5632,7 @@
         <v>42</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>10</v>
@@ -5618,7 +5657,7 @@
         <v>42</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>10</v>
@@ -5632,7 +5671,7 @@
         <v>42</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>10</v>
@@ -5646,7 +5685,7 @@
         <v>42</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>10</v>
@@ -5660,7 +5699,7 @@
         <v>42</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>10</v>
@@ -5674,7 +5713,7 @@
         <v>42</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -5688,7 +5727,7 @@
         <v>42</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -5702,7 +5741,7 @@
         <v>42</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>10</v>
@@ -5716,7 +5755,7 @@
         <v>42</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>10</v>
@@ -5730,7 +5769,7 @@
         <v>42</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>10</v>
@@ -5744,7 +5783,7 @@
         <v>42</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>5</v>
@@ -5764,7 +5803,7 @@
         <v>45</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>10</v>
@@ -5777,7 +5816,7 @@
       <c r="A32" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
       <c r="C32" s="1" t="s">
@@ -5787,7 +5826,7 @@
         <v>49</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>7</v>
@@ -5810,7 +5849,7 @@
         <v>52</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>10</v>
@@ -5823,7 +5862,7 @@
       <c r="A34" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="14" t="s">
         <v>56</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -5833,7 +5872,7 @@
         <v>55</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>10</v>
@@ -5858,7 +5897,7 @@
         <v>55</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>10</v>
@@ -5872,7 +5911,7 @@
         <v>55</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>10</v>
@@ -5886,7 +5925,7 @@
         <v>55</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>10</v>
@@ -5900,7 +5939,7 @@
         <v>55</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>10</v>
@@ -5914,7 +5953,7 @@
         <v>55</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>10</v>
@@ -5928,7 +5967,7 @@
         <v>55</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>7</v>
@@ -5948,7 +5987,7 @@
         <v>58</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>9</v>
@@ -5961,7 +6000,7 @@
       <c r="A42" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="10" t="s">
         <v>62</v>
       </c>
       <c r="C42" s="1" t="s">
@@ -5971,7 +6010,7 @@
         <v>61</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>10</v>
@@ -5994,7 +6033,7 @@
         <v>64</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F43" s="1" t="n">
         <v>10</v>
@@ -6017,7 +6056,7 @@
         <v>67</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>10</v>
@@ -6040,7 +6079,7 @@
         <v>70</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>9</v>
@@ -6065,7 +6104,7 @@
         <v>70</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F46" s="1" t="n">
         <v>9</v>
@@ -6079,7 +6118,7 @@
         <v>70</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>9</v>
@@ -6093,7 +6132,7 @@
         <v>70</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F48" s="1" t="n">
         <v>5</v>
@@ -6113,7 +6152,7 @@
         <v>73</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="F49" s="1" t="n">
         <v>8</v>
@@ -6138,7 +6177,7 @@
         <v>73</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F50" s="1" t="n">
         <v>6</v>
@@ -6148,7 +6187,7 @@
       <c r="A51" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B51" s="10" t="s">
+      <c r="B51" s="14" t="s">
         <v>76</v>
       </c>
       <c r="C51" s="1" t="s">
@@ -6158,7 +6197,7 @@
         <v>24</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F51" s="1" t="n">
         <v>10</v>
@@ -6183,7 +6222,7 @@
         <v>24</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F52" s="1" t="n">
         <v>3</v>
@@ -6231,16 +6270,16 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6421,7 +6460,7 @@
       <c r="A16" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -6680,7 +6719,7 @@
       <c r="A34" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="10" t="s">
         <v>37</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -7078,7 +7117,7 @@
       <c r="A64" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B64" s="9" t="s">
+      <c r="B64" s="10" t="s">
         <v>50</v>
       </c>
       <c r="C64" s="1" t="s">
@@ -7222,7 +7261,7 @@
       <c r="A74" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B74" s="10" t="s">
+      <c r="B74" s="14" t="s">
         <v>56</v>
       </c>
       <c r="C74" s="1" t="s">
@@ -7358,7 +7397,7 @@
       <c r="A84" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B84" s="9" t="s">
+      <c r="B84" s="10" t="s">
         <v>62</v>
       </c>
       <c r="C84" s="1" t="s">
@@ -7614,7 +7653,7 @@
       <c r="A101" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B101" s="10" t="s">
+      <c r="B101" s="14" t="s">
         <v>76</v>
       </c>
       <c r="C101" s="1" t="s">
@@ -7728,7 +7767,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Z23"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr defaultColWidth="9.58203125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.43"/>
@@ -7736,6 +7775,7 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="11" min="3" style="1" width="9.34"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="12" min="12" style="1" width="10.95"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="20" min="13" style="1" width="9.58"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="9.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7749,6 +7789,12 @@
         <v>82</v>
       </c>
       <c r="U1" s="1"/>
+      <c r="AB1" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC1" s="0" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -7823,8 +7869,17 @@
       <c r="Z2" s="1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA2" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB2" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC2" s="11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
@@ -7855,7 +7910,7 @@
       <c r="L3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="M3" s="8" t="n">
+      <c r="M3" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(L3,G3,E3,C3),0)</f>
         <v>4</v>
       </c>
@@ -7869,7 +7924,7 @@
       <c r="Q3" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="R3" s="8" t="n">
+      <c r="R3" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(M3,O3:Q3),0)</f>
         <v>5</v>
       </c>
@@ -7895,12 +7950,12 @@
         <f aca="false">W3+X3/2</f>
         <v>7</v>
       </c>
-      <c r="Z3" s="8" t="n">
+      <c r="Z3" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U3,V3,Y3),0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
@@ -7926,7 +7981,7 @@
         <f aca="false">I4+K4/2</f>
         <v>10</v>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="M4" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(L4,G4,E4,C4),0)</f>
         <v>9</v>
       </c>
@@ -7940,7 +7995,7 @@
       <c r="Q4" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="R4" s="8" t="n">
+      <c r="R4" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(M4,O4:Q4),0)</f>
         <v>9</v>
       </c>
@@ -7966,16 +8021,16 @@
         <f aca="false">W4+X4/2</f>
         <v>8</v>
       </c>
-      <c r="Z4" s="8" t="n">
+      <c r="Z4" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U4,V4,Y4),0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="1" t="n">
@@ -7997,7 +8052,7 @@
         <f aca="false">I5+K5/2</f>
         <v>9</v>
       </c>
-      <c r="M5" s="8" t="n">
+      <c r="M5" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(L5,G5,E5,C5),0)</f>
         <v>8</v>
       </c>
@@ -8011,7 +8066,7 @@
       <c r="Q5" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="R5" s="8" t="n">
+      <c r="R5" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(M5,O5:Q5),0)</f>
         <v>9</v>
       </c>
@@ -8037,12 +8092,12 @@
         <f aca="false">W5+X5/2</f>
         <v>10</v>
       </c>
-      <c r="Z5" s="8" t="n">
+      <c r="Z5" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U5,V5,Y5),0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
@@ -8068,7 +8123,7 @@
         <f aca="false">I6+K6/2</f>
         <v>10</v>
       </c>
-      <c r="M6" s="8" t="n">
+      <c r="M6" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(L6,G6,E6,C6),0)</f>
         <v>8</v>
       </c>
@@ -8082,7 +8137,7 @@
       <c r="Q6" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="R6" s="8" t="n">
+      <c r="R6" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(M6,O6:Q6),0)</f>
         <v>7</v>
       </c>
@@ -8108,12 +8163,12 @@
         <f aca="false">W6+X6/2</f>
         <v>5</v>
       </c>
-      <c r="Z6" s="8" t="n">
+      <c r="Z6" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U6,V6,Y6),0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
@@ -8139,7 +8194,7 @@
         <f aca="false">I7+K7/2</f>
         <v>8.5</v>
       </c>
-      <c r="M7" s="8" t="n">
+      <c r="M7" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(L7,G7,E7,C7),0)</f>
         <v>9</v>
       </c>
@@ -8153,7 +8208,7 @@
       <c r="Q7" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="R7" s="8" t="n">
+      <c r="R7" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(M7,O7:Q7),0)</f>
         <v>9</v>
       </c>
@@ -8179,84 +8234,94 @@
         <f aca="false">W7+X7/2</f>
         <v>8</v>
       </c>
-      <c r="Z7" s="8" t="n">
+      <c r="Z7" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U7,V7,Y7),0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
+    <row r="8" s="13" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I8" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="K8" s="1" t="n">
+      <c r="C8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L8" s="1" t="n">
+      <c r="L8" s="2" t="n">
         <f aca="false">I8+K8/2</f>
         <v>11</v>
       </c>
-      <c r="M8" s="8" t="n">
+      <c r="M8" s="12" t="n">
         <f aca="false">ROUND(AVERAGE(L8,G8,E8,C8),0)</f>
         <v>10</v>
       </c>
-      <c r="N8" s="1" t="str">
+      <c r="N8" s="2" t="str">
         <f aca="false">IF(M8&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="O8" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q8" s="1" t="n">
+      <c r="O8" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="8" t="n">
+      <c r="R8" s="12" t="n">
         <f aca="false">ROUND(AVERAGE(M8,O8:Q8),0)</f>
         <v>7</v>
       </c>
-      <c r="S8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W8" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="X8" s="1" t="n">
+      <c r="S8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="Y8" s="1" t="n">
+      <c r="Y8" s="2" t="n">
         <f aca="false">W8+X8/2</f>
-        <v>2</v>
-      </c>
-      <c r="Z8" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z8" s="12" t="n">
         <f aca="false">ROUND(AVERAGE(U8,V8,Y8),0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA8" s="13" t="n">
+        <f aca="false">Z8*6/10</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" s="13" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>34</v>
       </c>
       <c r="C9" s="2" t="n">
@@ -8283,63 +8348,64 @@
       <c r="J9" s="5" t="n">
         <v>45855</v>
       </c>
-      <c r="K9" s="1" t="n">
+      <c r="K9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L9" s="1" t="n">
+      <c r="L9" s="2" t="n">
         <f aca="false">I9+K9/2</f>
         <v>7</v>
       </c>
-      <c r="M9" s="8" t="n">
+      <c r="M9" s="12" t="n">
         <f aca="false">ROUND(AVERAGE(L9,G9,E9,C9),0)</f>
         <v>6</v>
       </c>
-      <c r="N9" s="1" t="str">
+      <c r="N9" s="2" t="str">
         <f aca="false">IF(M9&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="O9" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q9" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="R9" s="8" t="n">
+      <c r="O9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="R9" s="12" t="n">
         <f aca="false">ROUND(AVERAGE(M9,O9:Q9),0)</f>
         <v>8</v>
       </c>
-      <c r="S9" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" s="4" t="n">
+      <c r="S9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" s="5" t="n">
         <v>45834</v>
       </c>
-      <c r="U9" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="V9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W9" s="1" t="n">
+      <c r="U9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="X9" s="1" t="n">
+      <c r="X9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="Y9" s="1" t="n">
+      <c r="Y9" s="2" t="n">
         <f aca="false">W9+X9/2</f>
         <v>6</v>
       </c>
-      <c r="Z9" s="8" t="n">
+      <c r="Z9" s="12" t="n">
         <f aca="false">ROUND(AVERAGE(U9,V9,Y9),0)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="10" t="s">
         <v>37</v>
       </c>
       <c r="C10" s="1" t="n">
@@ -8361,7 +8427,7 @@
         <f aca="false">I10+K10/2</f>
         <v>12</v>
       </c>
-      <c r="M10" s="8" t="n">
+      <c r="M10" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(L10,G10,E10,C10),0)</f>
         <v>10</v>
       </c>
@@ -8375,7 +8441,7 @@
       <c r="Q10" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="R10" s="8" t="n">
+      <c r="R10" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(M10,O10:Q10),0)</f>
         <v>10</v>
       </c>
@@ -8398,12 +8464,12 @@
         <f aca="false">W10+X10/2</f>
         <v>11.5</v>
       </c>
-      <c r="Z10" s="8" t="n">
+      <c r="Z10" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U10,V10,Y10),0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
@@ -8435,7 +8501,7 @@
         <f aca="false">I11+K11/2</f>
         <v>2.5</v>
       </c>
-      <c r="M11" s="8" t="n">
+      <c r="M11" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(L11,G11,E11,C11),0)</f>
         <v>5</v>
       </c>
@@ -8449,7 +8515,7 @@
       <c r="Q11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="R11" s="8" t="n">
+      <c r="R11" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(M11,O11:Q11),0)</f>
         <v>7</v>
       </c>
@@ -8472,12 +8538,12 @@
         <f aca="false">W11+X11/2</f>
         <v>10</v>
       </c>
-      <c r="Z11" s="8" t="n">
+      <c r="Z11" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U11,V11,Y11),0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
@@ -8503,7 +8569,7 @@
         <f aca="false">I12+K12/2</f>
         <v>12</v>
       </c>
-      <c r="M12" s="8" t="n">
+      <c r="M12" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(L12,G12,E12,C12),0)</f>
         <v>10</v>
       </c>
@@ -8517,7 +8583,7 @@
       <c r="Q12" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="R12" s="8" t="n">
+      <c r="R12" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(M12,O12:Q12),0)</f>
         <v>9</v>
       </c>
@@ -8540,12 +8606,12 @@
         <f aca="false">W12+X12/2</f>
         <v>10</v>
       </c>
-      <c r="Z12" s="8" t="n">
+      <c r="Z12" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U12,V12,Y12),0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
@@ -8571,7 +8637,7 @@
         <f aca="false">I13+K13/2</f>
         <v>10.5</v>
       </c>
-      <c r="M13" s="8" t="n">
+      <c r="M13" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(L13,G13,E13,C13),0)</f>
         <v>9</v>
       </c>
@@ -8585,7 +8651,7 @@
       <c r="Q13" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="8" t="n">
+      <c r="R13" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(M13,O13:Q13),0)</f>
         <v>9</v>
       </c>
@@ -8611,16 +8677,16 @@
         <f aca="false">W13+X13/2</f>
         <v>8</v>
       </c>
-      <c r="Z13" s="8" t="n">
+      <c r="Z13" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U13,V13,Y13),0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="10" t="s">
         <v>50</v>
       </c>
       <c r="C14" s="1" t="n">
@@ -8642,7 +8708,7 @@
         <f aca="false">I14+K14/2</f>
         <v>10</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(L14,G14,E14,C14),0)</f>
         <v>8</v>
       </c>
@@ -8656,7 +8722,7 @@
       <c r="Q14" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="R14" s="8" t="n">
+      <c r="R14" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(M14,O14:Q14),0)</f>
         <v>8</v>
       </c>
@@ -8679,12 +8745,12 @@
         <f aca="false">W14+X14/2</f>
         <v>10</v>
       </c>
-      <c r="Z14" s="8" t="n">
+      <c r="Z14" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U14,V14,Y14),0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
@@ -8710,7 +8776,7 @@
         <f aca="false">I15+K15/2</f>
         <v>11</v>
       </c>
-      <c r="M15" s="8" t="n">
+      <c r="M15" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(L15,G15,E15,C15),0)</f>
         <v>8</v>
       </c>
@@ -8724,7 +8790,7 @@
       <c r="Q15" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="R15" s="8" t="n">
+      <c r="R15" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(M15,O15:Q15),0)</f>
         <v>8</v>
       </c>
@@ -8747,16 +8813,16 @@
         <f aca="false">W15+X15/2</f>
         <v>7</v>
       </c>
-      <c r="Z15" s="8" t="n">
+      <c r="Z15" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U15,V15,Y15),0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="14" t="s">
         <v>56</v>
       </c>
       <c r="C16" s="1" t="n">
@@ -8778,7 +8844,7 @@
         <f aca="false">I16+K16/2</f>
         <v>12</v>
       </c>
-      <c r="M16" s="8" t="n">
+      <c r="M16" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(L16,G16,E16,C16),0)</f>
         <v>10</v>
       </c>
@@ -8792,7 +8858,7 @@
       <c r="Q16" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="R16" s="8" t="n">
+      <c r="R16" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(M16,O16:Q16),0)</f>
         <v>10</v>
       </c>
@@ -8818,12 +8884,12 @@
         <f aca="false">W16+X16/2</f>
         <v>7</v>
       </c>
-      <c r="Z16" s="8" t="n">
+      <c r="Z16" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U16,V16,Y16),0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
@@ -8849,7 +8915,7 @@
         <f aca="false">I17+K17/2</f>
         <v>11.5</v>
       </c>
-      <c r="M17" s="8" t="n">
+      <c r="M17" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(L17,G17,E17,C17),0)</f>
         <v>8</v>
       </c>
@@ -8863,7 +8929,7 @@
       <c r="Q17" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="R17" s="8" t="n">
+      <c r="R17" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(M17,O17:Q17),0)</f>
         <v>8</v>
       </c>
@@ -8886,16 +8952,16 @@
         <f aca="false">W17+X17/2</f>
         <v>7</v>
       </c>
-      <c r="Z17" s="8" t="n">
+      <c r="Z17" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U17,V17,Y17),0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="10" t="s">
         <v>62</v>
       </c>
       <c r="C18" s="1" t="n">
@@ -8917,7 +8983,7 @@
         <f aca="false">I18+K18/2</f>
         <v>11.5</v>
       </c>
-      <c r="M18" s="8" t="n">
+      <c r="M18" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(L18,G18,E18,C18),0)</f>
         <v>9</v>
       </c>
@@ -8931,7 +8997,7 @@
       <c r="Q18" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="R18" s="8" t="n">
+      <c r="R18" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(M18,O18:Q18),0)</f>
         <v>6</v>
       </c>
@@ -8954,12 +9020,12 @@
         <f aca="false">W18+X18/2</f>
         <v>7.5</v>
       </c>
-      <c r="Z18" s="8" t="n">
+      <c r="Z18" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U18,V18,Y18),0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
@@ -8985,7 +9051,7 @@
         <f aca="false">I19+K19/2</f>
         <v>12</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(L19,G19,E19,C19),0)</f>
         <v>9</v>
       </c>
@@ -8999,7 +9065,7 @@
       <c r="Q19" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="R19" s="8" t="n">
+      <c r="R19" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(M19,O19:Q19),0)</f>
         <v>10</v>
       </c>
@@ -9022,80 +9088,90 @@
         <f aca="false">W19+X19/2</f>
         <v>10</v>
       </c>
-      <c r="Z19" s="8" t="n">
+      <c r="Z19" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U19,V19,Y19),0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="n">
+    <row r="20" s="13" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C20" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="G20" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I20" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="K20" s="1" t="n">
+      <c r="C20" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="L20" s="1" t="n">
+      <c r="L20" s="2" t="n">
         <f aca="false">I20+K20/2</f>
         <v>11.5</v>
       </c>
-      <c r="M20" s="8" t="n">
+      <c r="M20" s="12" t="n">
         <f aca="false">ROUND(AVERAGE(L20,G20,E20,C20),0)</f>
         <v>10</v>
       </c>
-      <c r="N20" s="1" t="str">
+      <c r="N20" s="2" t="str">
         <f aca="false">IF(M20&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="O20" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q20" s="1" t="n">
+      <c r="O20" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="R20" s="8" t="n">
+      <c r="R20" s="12" t="n">
         <f aca="false">ROUND(AVERAGE(M20,O20:Q20),0)</f>
         <v>9</v>
       </c>
-      <c r="S20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="X20" s="1" t="n">
+      <c r="S20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V20" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="W20" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="Y20" s="1" t="n">
+      <c r="Y20" s="2" t="n">
         <f aca="false">W20+X20/2</f>
-        <v>1</v>
-      </c>
-      <c r="Z20" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z20" s="12" t="n">
         <f aca="false">ROUND(AVERAGE(U20,V20,Y20),0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>10</v>
+      </c>
+      <c r="AA20" s="13" t="n">
+        <f aca="false">Z20*6/10</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
@@ -9121,7 +9197,7 @@
         <f aca="false">I21+K21/2</f>
         <v>11</v>
       </c>
-      <c r="M21" s="8" t="n">
+      <c r="M21" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(L21,G21,E21,C21),0)</f>
         <v>9</v>
       </c>
@@ -9135,7 +9211,7 @@
       <c r="Q21" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="R21" s="8" t="n">
+      <c r="R21" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(M21,O21:Q21),0)</f>
         <v>8</v>
       </c>
@@ -9158,84 +9234,94 @@
         <f aca="false">W21+X21/2</f>
         <v>9</v>
       </c>
-      <c r="Z21" s="8" t="n">
+      <c r="Z21" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U21,V21,Y21),0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="n">
+    <row r="22" s="13" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C22" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="1" t="n">
+      <c r="B22" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2"/>
+      <c r="G22" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I22" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="K22" s="1" t="n">
+      <c r="H22" s="2"/>
+      <c r="I22" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="L22" s="1" t="n">
+      <c r="L22" s="2" t="n">
         <f aca="false">I22+K22/2</f>
         <v>9</v>
       </c>
-      <c r="M22" s="8" t="n">
+      <c r="M22" s="12" t="n">
         <f aca="false">ROUND(AVERAGE(L22,G22,E22,C22),0)</f>
         <v>3</v>
       </c>
-      <c r="N22" s="1" t="str">
+      <c r="N22" s="2" t="str">
         <f aca="false">IF(M22&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="O22" s="1" t="n">
+      <c r="O22" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="Q22" s="1" t="n">
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="R22" s="8" t="n">
+      <c r="R22" s="12" t="n">
         <f aca="false">ROUND(AVERAGE(M22,O22:Q22),0)</f>
         <v>4</v>
       </c>
-      <c r="S22" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V22" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W22" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="X22" s="1" t="n">
+      <c r="S22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="W22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="Y22" s="1" t="n">
+      <c r="Y22" s="2" t="n">
         <f aca="false">W22+X22/2</f>
-        <v>1</v>
-      </c>
-      <c r="Z22" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z22" s="12" t="n">
         <f aca="false">ROUND(AVERAGE(U22,V22,Y22),0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>10</v>
+      </c>
+      <c r="AA22" s="13" t="n">
+        <f aca="false">Z22*6/10</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="14" t="s">
         <v>76</v>
       </c>
       <c r="C23" s="1" t="n">
@@ -9257,7 +9343,7 @@
         <f aca="false">I23+K23/2</f>
         <v>10</v>
       </c>
-      <c r="M23" s="8" t="n">
+      <c r="M23" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(L23,G23,E23,C23),0)</f>
         <v>9</v>
       </c>
@@ -9271,7 +9357,7 @@
       <c r="Q23" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="R23" s="8" t="n">
+      <c r="R23" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(M23,O23:Q23),0)</f>
         <v>8</v>
       </c>
@@ -9294,7 +9380,7 @@
         <f aca="false">W23+X23/2</f>
         <v>7</v>
       </c>
-      <c r="Z23" s="8" t="n">
+      <c r="Z23" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U23,V23,Y23),0)</f>
         <v>9</v>
       </c>
@@ -9363,10 +9449,10 @@
       <c r="B1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="11" t="n">
+      <c r="C1" s="16" t="n">
         <v>45729</v>
       </c>
-      <c r="D1" s="11" t="n">
+      <c r="D1" s="16" t="n">
         <v>45736</v>
       </c>
       <c r="E1" s="4" t="n">
@@ -9984,22 +10070,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>94</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10125,10 +10211,10 @@
         <v>40</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>3</v>
@@ -10232,10 +10318,10 @@
         <v>62</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>8</v>
@@ -10255,10 +10341,10 @@
         <v>65</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>9</v>
@@ -10280,10 +10366,10 @@
         <v>65</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>8</v>
@@ -10294,10 +10380,10 @@
         <v>65</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>7</v>
@@ -10308,10 +10394,10 @@
         <v>65</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>7</v>
@@ -10322,10 +10408,10 @@
         <v>65</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>6</v>
@@ -10364,7 +10450,7 @@
         <v>20</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>1</v>
@@ -10445,19 +10531,19 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>94</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10486,7 +10572,7 @@
         <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>4</v>
@@ -10511,7 +10597,7 @@
         <v>18</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>9</v>
@@ -10525,7 +10611,7 @@
         <v>18</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>10</v>
@@ -10535,7 +10621,7 @@
       <c r="A6" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -10545,7 +10631,7 @@
         <v>21</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>9</v>
@@ -10570,7 +10656,7 @@
         <v>21</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>8</v>
@@ -10584,7 +10670,7 @@
         <v>21</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>6</v>
@@ -10598,7 +10684,7 @@
         <v>21</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>2</v>
@@ -10618,7 +10704,7 @@
         <v>24</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>7</v>
@@ -10643,7 +10729,7 @@
         <v>24</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>7</v>
@@ -10663,7 +10749,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>8</v>
@@ -10686,7 +10772,7 @@
         <v>30</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>10</v>
@@ -10713,7 +10799,7 @@
       <c r="A15" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="10" t="s">
         <v>37</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -10723,7 +10809,7 @@
         <v>36</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>2</v>
@@ -10748,7 +10834,7 @@
         <v>36</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>5</v>
@@ -10762,7 +10848,7 @@
         <v>36</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>7</v>
@@ -10776,7 +10862,7 @@
         <v>36</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>8</v>
@@ -10790,7 +10876,7 @@
         <v>36</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>8</v>
@@ -10804,7 +10890,7 @@
         <v>36</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>8</v>
@@ -10818,7 +10904,7 @@
         <v>36</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>9</v>
@@ -10832,7 +10918,7 @@
         <v>36</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>9</v>
@@ -10846,7 +10932,7 @@
         <v>36</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>9</v>
@@ -10860,7 +10946,7 @@
         <v>36</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>9</v>
@@ -10874,7 +10960,7 @@
         <v>36</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -10894,7 +10980,7 @@
         <v>39</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>3</v>
@@ -10919,7 +11005,7 @@
         <v>39</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>3</v>
@@ -10933,7 +11019,7 @@
         <v>39</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>4</v>
@@ -10953,7 +11039,7 @@
         <v>42</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>6</v>
@@ -10978,7 +11064,7 @@
         <v>42</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>9</v>
@@ -10992,7 +11078,7 @@
         <v>42</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>9</v>
@@ -11006,7 +11092,7 @@
         <v>42</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>9</v>
@@ -11020,7 +11106,7 @@
         <v>42</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>10</v>
@@ -11034,7 +11120,7 @@
         <v>42</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>10</v>
@@ -11048,7 +11134,7 @@
         <v>42</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>10</v>
@@ -11062,7 +11148,7 @@
         <v>42</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>10</v>
@@ -11076,7 +11162,7 @@
         <v>42</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>10</v>
@@ -11096,7 +11182,7 @@
         <v>45</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>7</v>
@@ -11121,7 +11207,7 @@
         <v>45</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>8</v>
@@ -11131,7 +11217,7 @@
       <c r="A40" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="10" t="s">
         <v>50</v>
       </c>
       <c r="C40" s="1" t="s">
@@ -11141,7 +11227,7 @@
         <v>49</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>8</v>
@@ -11164,7 +11250,7 @@
         <v>52</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>7</v>
@@ -11189,7 +11275,7 @@
         <v>52</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>7</v>
@@ -11203,7 +11289,7 @@
         <v>52</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F43" s="1" t="n">
         <v>8</v>
@@ -11217,7 +11303,7 @@
         <v>52</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>10</v>
@@ -11227,7 +11313,7 @@
       <c r="A45" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="14" t="s">
         <v>56</v>
       </c>
       <c r="C45" s="1" t="s">
@@ -11237,7 +11323,7 @@
         <v>55</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>10</v>
@@ -11260,7 +11346,7 @@
         <v>58</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F46" s="1" t="n">
         <v>9</v>
@@ -11273,7 +11359,7 @@
       <c r="A47" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="10" t="s">
         <v>62</v>
       </c>
       <c r="C47" s="1" t="s">
@@ -11283,7 +11369,7 @@
         <v>61</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>8</v>
@@ -11306,7 +11392,7 @@
         <v>64</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F48" s="1" t="n">
         <v>6</v>
@@ -11331,7 +11417,7 @@
         <v>64</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F49" s="1" t="n">
         <v>7</v>
@@ -11345,7 +11431,7 @@
         <v>64</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F50" s="1" t="n">
         <v>7</v>
@@ -11359,7 +11445,7 @@
         <v>64</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F51" s="1" t="n">
         <v>8</v>
@@ -11373,7 +11459,7 @@
         <v>64</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F52" s="1" t="n">
         <v>9</v>
@@ -11393,7 +11479,7 @@
         <v>67</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F53" s="1" t="n">
         <v>10</v>
@@ -11416,7 +11502,7 @@
         <v>70</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F54" s="1" t="n">
         <v>9</v>
@@ -11443,7 +11529,7 @@
       <c r="A56" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B56" s="10" t="s">
+      <c r="B56" s="14" t="s">
         <v>76</v>
       </c>
       <c r="C56" s="1" t="s">
@@ -11453,7 +11539,7 @@
         <v>24</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F56" s="1" t="n">
         <v>3</v>
@@ -11478,7 +11564,7 @@
         <v>24</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F57" s="1" t="n">
         <v>6</v>
@@ -11492,7 +11578,7 @@
         <v>24</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>6</v>
@@ -11506,7 +11592,7 @@
         <v>24</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F59" s="1" t="n">
         <v>7</v>
@@ -11520,7 +11606,7 @@
         <v>24</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F60" s="1" t="n">
         <v>9</v>
@@ -11534,7 +11620,7 @@
         <v>24</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>9</v>
@@ -11587,22 +11673,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>94</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11826,10 +11912,10 @@
         <v>62</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>10</v>
@@ -11849,10 +11935,10 @@
         <v>65</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>10</v>
@@ -11874,10 +11960,10 @@
         <v>65</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>8</v>
@@ -11888,10 +11974,10 @@
         <v>65</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>8</v>
@@ -11902,10 +11988,10 @@
         <v>65</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>8</v>
@@ -11944,7 +12030,7 @@
         <v>20</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>1</v>
@@ -12023,19 +12109,19 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>94</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12066,7 +12152,7 @@
         <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>10</v>
@@ -12091,7 +12177,7 @@
         <v>18</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>9</v>
@@ -12105,7 +12191,7 @@
         <v>18</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>0</v>
@@ -12115,7 +12201,7 @@
       <c r="A6" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -12125,7 +12211,7 @@
         <v>21</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>9</v>
@@ -12150,7 +12236,7 @@
         <v>21</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>7</v>
@@ -12164,7 +12250,7 @@
         <v>21</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>6</v>
@@ -12178,7 +12264,7 @@
         <v>21</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>6</v>
@@ -12198,7 +12284,7 @@
         <v>24</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>7</v>
@@ -12221,7 +12307,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>10</v>
@@ -12246,7 +12332,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>10</v>
@@ -12260,7 +12346,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>9</v>
@@ -12274,7 +12360,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>7</v>
@@ -12288,7 +12374,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>6</v>
@@ -12302,7 +12388,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>5</v>
@@ -12316,7 +12402,7 @@
         <v>27</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>5</v>
@@ -12330,7 +12416,7 @@
         <v>27</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>5</v>
@@ -12350,7 +12436,7 @@
         <v>30</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>10</v>
@@ -12377,7 +12463,7 @@
       <c r="A21" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="10" t="s">
         <v>37</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -12387,7 +12473,7 @@
         <v>36</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>10</v>
@@ -12424,7 +12510,7 @@
         <v>42</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>10</v>
@@ -12449,7 +12535,7 @@
         <v>42</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>10</v>
@@ -12463,7 +12549,7 @@
         <v>42</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -12477,7 +12563,7 @@
         <v>42</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -12491,7 +12577,7 @@
         <v>42</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>10</v>
@@ -12505,7 +12591,7 @@
         <v>42</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>10</v>
@@ -12519,7 +12605,7 @@
         <v>42</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>10</v>
@@ -12533,7 +12619,7 @@
         <v>42</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>10</v>
@@ -12547,7 +12633,7 @@
         <v>42</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>10</v>
@@ -12561,7 +12647,7 @@
         <v>42</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>10</v>
@@ -12575,7 +12661,7 @@
         <v>42</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>10</v>
@@ -12589,7 +12675,7 @@
         <v>42</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>10</v>
@@ -12603,7 +12689,7 @@
         <v>42</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>8</v>
@@ -12617,7 +12703,7 @@
         <v>42</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>8</v>
@@ -12631,7 +12717,7 @@
         <v>42</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>7</v>
@@ -12651,7 +12737,7 @@
         <v>45</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>8</v>
@@ -12664,7 +12750,7 @@
       <c r="A39" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="10" t="s">
         <v>50</v>
       </c>
       <c r="C39" s="1" t="s">
@@ -12674,7 +12760,7 @@
         <v>49</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>8</v>
@@ -12697,7 +12783,7 @@
         <v>52</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>9</v>
@@ -12722,7 +12808,7 @@
         <v>52</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>7</v>
@@ -12736,7 +12822,7 @@
         <v>52</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>6</v>
@@ -12750,7 +12836,7 @@
         <v>52</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F43" s="1" t="n">
         <v>5</v>
@@ -12764,7 +12850,7 @@
         <v>52</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>4</v>
@@ -12778,7 +12864,7 @@
         <v>52</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>3</v>
@@ -12788,7 +12874,7 @@
       <c r="A46" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B46" s="14" t="s">
         <v>56</v>
       </c>
       <c r="C46" s="1" t="s">
@@ -12798,7 +12884,7 @@
         <v>55</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F46" s="1" t="n">
         <v>10</v>
@@ -12821,7 +12907,7 @@
         <v>58</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>7</v>
@@ -12834,7 +12920,7 @@
       <c r="A48" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="10" t="s">
         <v>62</v>
       </c>
       <c r="C48" s="1" t="s">
@@ -12844,7 +12930,7 @@
         <v>61</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F48" s="1" t="n">
         <v>10</v>
@@ -12867,7 +12953,7 @@
         <v>64</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F49" s="1" t="n">
         <v>10</v>
@@ -12892,7 +12978,7 @@
         <v>64</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F50" s="1" t="n">
         <v>8</v>
@@ -12906,7 +12992,7 @@
         <v>64</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F51" s="1" t="n">
         <v>8</v>
@@ -12920,7 +13006,7 @@
         <v>64</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F52" s="1" t="n">
         <v>8</v>
@@ -12940,7 +13026,7 @@
         <v>67</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F53" s="1" t="n">
         <v>10</v>
@@ -12963,7 +13049,7 @@
         <v>70</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F54" s="1" t="n">
         <v>10</v>
@@ -12988,7 +13074,7 @@
         <v>70</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F55" s="1" t="n">
         <v>8</v>
@@ -13002,7 +13088,7 @@
         <v>70</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F56" s="1" t="n">
         <v>6</v>
@@ -13016,7 +13102,7 @@
         <v>70</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F57" s="1" t="n">
         <v>1</v>
@@ -13040,7 +13126,7 @@
       <c r="A59" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="B59" s="14" t="s">
         <v>76</v>
       </c>
       <c r="C59" s="1" t="s">
@@ -13050,7 +13136,7 @@
         <v>24</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F59" s="1" t="n">
         <v>10</v>
@@ -13075,7 +13161,7 @@
         <v>24</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F60" s="1" t="n">
         <v>10</v>
@@ -13089,7 +13175,7 @@
         <v>24</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>9</v>
@@ -13103,7 +13189,7 @@
         <v>24</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>7</v>
@@ -13117,7 +13203,7 @@
         <v>24</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F63" s="1" t="n">
         <v>5</v>
@@ -13131,7 +13217,7 @@
         <v>24</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F64" s="1" t="n">
         <v>5</v>
@@ -13176,22 +13262,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>94</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13205,10 +13291,10 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>5</v>
@@ -13230,10 +13316,10 @@
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>3</v>
@@ -13244,10 +13330,10 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>3</v>
@@ -13264,10 +13350,10 @@
         <v>19</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>7</v>
@@ -13289,10 +13375,10 @@
         <v>19</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>3</v>
@@ -13309,10 +13395,10 @@
         <v>22</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>8</v>
@@ -13334,10 +13420,10 @@
         <v>22</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>7</v>
@@ -13348,10 +13434,10 @@
         <v>22</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>6</v>
@@ -13362,10 +13448,10 @@
         <v>22</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>3</v>
@@ -13376,10 +13462,10 @@
         <v>22</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>2</v>
@@ -13396,10 +13482,10 @@
         <v>25</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>8</v>
@@ -13421,10 +13507,10 @@
         <v>25</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>6</v>
@@ -13435,10 +13521,10 @@
         <v>25</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>6</v>
@@ -13449,10 +13535,10 @@
         <v>25</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>4</v>
@@ -13463,10 +13549,10 @@
         <v>25</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>3</v>
@@ -13483,10 +13569,10 @@
         <v>28</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>8</v>
@@ -13508,10 +13594,10 @@
         <v>28</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>3</v>
@@ -13528,10 +13614,10 @@
         <v>31</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>5</v>
@@ -13553,10 +13639,10 @@
         <v>31</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>3</v>
@@ -13567,10 +13653,10 @@
         <v>31</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>2</v>
@@ -13581,10 +13667,10 @@
         <v>31</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>1</v>
@@ -13601,10 +13687,10 @@
         <v>34</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>3</v>
@@ -13624,10 +13710,10 @@
         <v>37</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>10</v>
@@ -13649,10 +13735,10 @@
         <v>37</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>7</v>
@@ -13663,10 +13749,10 @@
         <v>37</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>7</v>
@@ -13677,10 +13763,10 @@
         <v>37</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>6</v>
@@ -13691,10 +13777,10 @@
         <v>37</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>5</v>
@@ -13705,10 +13791,10 @@
         <v>37</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>4</v>
@@ -13719,10 +13805,10 @@
         <v>37</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>4</v>
@@ -13733,10 +13819,10 @@
         <v>37</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>3</v>
@@ -13747,10 +13833,10 @@
         <v>37</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>2</v>
@@ -13767,10 +13853,10 @@
         <v>40</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>7</v>
@@ -13792,10 +13878,10 @@
         <v>40</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>6</v>
@@ -13806,10 +13892,10 @@
         <v>40</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>5</v>
@@ -13820,10 +13906,10 @@
         <v>40</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>5</v>
@@ -13834,10 +13920,10 @@
         <v>40</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>5</v>
@@ -13848,10 +13934,10 @@
         <v>40</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>5</v>
@@ -13862,10 +13948,10 @@
         <v>40</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>4</v>
@@ -13876,10 +13962,10 @@
         <v>40</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>2</v>
@@ -13896,10 +13982,10 @@
         <v>43</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>10</v>
@@ -13921,10 +14007,10 @@
         <v>43</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>8</v>
@@ -13935,10 +14021,10 @@
         <v>43</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F43" s="1" t="n">
         <v>4</v>
@@ -13949,10 +14035,10 @@
         <v>43</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>3</v>
@@ -13963,10 +14049,10 @@
         <v>43</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>1</v>
@@ -13997,10 +14083,10 @@
         <v>50</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>8</v>
@@ -14022,10 +14108,10 @@
         <v>50</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F48" s="1" t="n">
         <v>7</v>
@@ -14036,10 +14122,10 @@
         <v>50</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F49" s="1" t="n">
         <v>7</v>
@@ -14050,10 +14136,10 @@
         <v>50</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F50" s="1" t="n">
         <v>7</v>
@@ -14064,10 +14150,10 @@
         <v>50</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F51" s="1" t="n">
         <v>5</v>
@@ -14078,10 +14164,10 @@
         <v>50</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F52" s="1" t="n">
         <v>3</v>
@@ -14098,10 +14184,10 @@
         <v>53</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F53" s="1" t="n">
         <v>7</v>
@@ -14121,10 +14207,10 @@
         <v>56</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F54" s="1" t="n">
         <v>8</v>
@@ -14146,10 +14232,10 @@
         <v>56</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F55" s="1" t="n">
         <v>6</v>
@@ -14160,10 +14246,10 @@
         <v>56</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F56" s="1" t="n">
         <v>6</v>
@@ -14174,10 +14260,10 @@
         <v>56</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F57" s="1" t="n">
         <v>5</v>
@@ -14188,10 +14274,10 @@
         <v>56</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>5</v>
@@ -14208,10 +14294,10 @@
         <v>59</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F59" s="1" t="n">
         <v>6</v>
@@ -14233,10 +14319,10 @@
         <v>59</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F60" s="1" t="n">
         <v>6</v>
@@ -14247,10 +14333,10 @@
         <v>59</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>6</v>
@@ -14261,10 +14347,10 @@
         <v>59</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>5</v>
@@ -14275,10 +14361,10 @@
         <v>59</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F63" s="1" t="n">
         <v>5</v>
@@ -14289,10 +14375,10 @@
         <v>59</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F64" s="1" t="n">
         <v>4</v>
@@ -14303,10 +14389,10 @@
         <v>59</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F65" s="1" t="n">
         <v>4</v>
@@ -14337,10 +14423,10 @@
         <v>65</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F67" s="1" t="n">
         <v>10</v>
@@ -14362,10 +14448,10 @@
         <v>65</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F68" s="1" t="n">
         <v>6</v>
@@ -14376,10 +14462,10 @@
         <v>65</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F69" s="1" t="n">
         <v>5</v>
@@ -14390,10 +14476,10 @@
         <v>65</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F70" s="1" t="n">
         <v>4</v>
@@ -14404,10 +14490,10 @@
         <v>65</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F71" s="1" t="n">
         <v>4</v>
@@ -14418,10 +14504,10 @@
         <v>65</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F72" s="1" t="n">
         <v>4</v>
@@ -14438,10 +14524,10 @@
         <v>68</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F73" s="1" t="n">
         <v>10</v>
@@ -14463,10 +14549,10 @@
         <v>68</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F74" s="1" t="n">
         <v>6</v>
@@ -14477,10 +14563,10 @@
         <v>68</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F75" s="1" t="n">
         <v>1</v>
@@ -14497,10 +14583,10 @@
         <v>71</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F76" s="1" t="n">
         <v>9</v>
@@ -14522,10 +14608,10 @@
         <v>71</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F77" s="1" t="n">
         <v>5</v>
@@ -14536,10 +14622,10 @@
         <v>71</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F78" s="1" t="n">
         <v>3</v>
@@ -14550,10 +14636,10 @@
         <v>71</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F79" s="1" t="n">
         <v>3</v>
@@ -14564,7 +14650,7 @@
         <v>20</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F80" s="1" t="n">
         <v>1</v>
@@ -14584,10 +14670,10 @@
         <v>74</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F81" s="1" t="n">
         <v>2</v>
@@ -14607,10 +14693,10 @@
         <v>76</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F82" s="1" t="n">
         <v>10</v>
@@ -14632,10 +14718,10 @@
         <v>76</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F83" s="1" t="n">
         <v>9</v>
@@ -14646,10 +14732,10 @@
         <v>76</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F84" s="1" t="n">
         <v>8</v>
@@ -14660,10 +14746,10 @@
         <v>76</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F85" s="1" t="n">
         <v>6</v>
@@ -14674,10 +14760,10 @@
         <v>76</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F86" s="1" t="n">
         <v>6</v>
@@ -14688,10 +14774,10 @@
         <v>76</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F87" s="1" t="n">
         <v>4</v>
@@ -14702,10 +14788,10 @@
         <v>76</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F88" s="1" t="n">
         <v>2</v>
@@ -14716,10 +14802,10 @@
         <v>76</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F89" s="1" t="n">
         <v>1</v>
@@ -14767,19 +14853,19 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>94</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14796,7 +14882,7 @@
         <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>5</v>
@@ -14821,7 +14907,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>3</v>
@@ -14835,7 +14921,7 @@
         <v>11</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>3</v>
@@ -14855,7 +14941,7 @@
         <v>18</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>10</v>
@@ -14880,7 +14966,7 @@
         <v>18</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>9</v>
@@ -14894,7 +14980,7 @@
         <v>18</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>7</v>
@@ -14908,7 +14994,7 @@
         <v>18</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>3</v>
@@ -14918,7 +15004,7 @@
       <c r="A9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -14928,7 +15014,7 @@
         <v>21</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>8</v>
@@ -14953,7 +15039,7 @@
         <v>21</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>7</v>
@@ -14967,7 +15053,7 @@
         <v>21</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>6</v>
@@ -14981,7 +15067,7 @@
         <v>21</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>3</v>
@@ -14995,7 +15081,7 @@
         <v>21</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>2</v>
@@ -15015,7 +15101,7 @@
         <v>24</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>8</v>
@@ -15040,7 +15126,7 @@
         <v>24</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>6</v>
@@ -15054,7 +15140,7 @@
         <v>24</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>6</v>
@@ -15068,7 +15154,7 @@
         <v>24</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>4</v>
@@ -15082,7 +15168,7 @@
         <v>24</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>3</v>
@@ -15096,7 +15182,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>10</v>
@@ -15116,7 +15202,7 @@
         <v>27</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>10</v>
@@ -15141,7 +15227,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>9</v>
@@ -15155,7 +15241,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>9</v>
@@ -15169,7 +15255,7 @@
         <v>27</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>8</v>
@@ -15183,7 +15269,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>8</v>
@@ -15197,7 +15283,7 @@
         <v>27</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>7</v>
@@ -15211,7 +15297,7 @@
         <v>27</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>7</v>
@@ -15225,7 +15311,7 @@
         <v>27</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>7</v>
@@ -15239,7 +15325,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>6</v>
@@ -15253,7 +15339,7 @@
         <v>27</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>6</v>
@@ -15267,7 +15353,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>6</v>
@@ -15281,7 +15367,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>5</v>
@@ -15295,7 +15381,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>5</v>
@@ -15309,7 +15395,7 @@
         <v>27</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>5</v>
@@ -15323,7 +15409,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>4</v>
@@ -15337,7 +15423,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>3</v>
@@ -15357,7 +15443,7 @@
         <v>30</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>10</v>
@@ -15382,7 +15468,7 @@
         <v>30</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>9</v>
@@ -15396,7 +15482,7 @@
         <v>30</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>5</v>
@@ -15410,7 +15496,7 @@
         <v>30</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>3</v>
@@ -15424,7 +15510,7 @@
         <v>30</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>2</v>
@@ -15438,7 +15524,7 @@
         <v>30</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>1</v>
@@ -15458,7 +15544,7 @@
         <v>33</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>3</v>
@@ -15471,7 +15557,7 @@
       <c r="A43" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="10" t="s">
         <v>37</v>
       </c>
       <c r="C43" s="1" t="s">
@@ -15481,7 +15567,7 @@
         <v>36</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F43" s="1" t="n">
         <v>10</v>
@@ -15506,7 +15592,7 @@
         <v>36</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>9</v>
@@ -15520,7 +15606,7 @@
         <v>36</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>7</v>
@@ -15534,7 +15620,7 @@
         <v>36</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="F46" s="1" t="n">
         <v>7</v>
@@ -15548,7 +15634,7 @@
         <v>36</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>6</v>
@@ -15562,7 +15648,7 @@
         <v>36</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F48" s="1" t="n">
         <v>6</v>
@@ -15576,7 +15662,7 @@
         <v>36</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F49" s="1" t="n">
         <v>5</v>
@@ -15590,7 +15676,7 @@
         <v>36</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F50" s="1" t="n">
         <v>4</v>
@@ -15604,7 +15690,7 @@
         <v>36</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F51" s="1" t="n">
         <v>4</v>
@@ -15618,7 +15704,7 @@
         <v>36</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F52" s="1" t="n">
         <v>3</v>
@@ -15632,7 +15718,7 @@
         <v>36</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F53" s="1" t="n">
         <v>2</v>
@@ -15652,7 +15738,7 @@
         <v>39</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F54" s="1" t="n">
         <v>7</v>
@@ -15677,7 +15763,7 @@
         <v>39</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F55" s="1" t="n">
         <v>6</v>
@@ -15691,7 +15777,7 @@
         <v>39</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="F56" s="1" t="n">
         <v>5</v>
@@ -15705,7 +15791,7 @@
         <v>39</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F57" s="1" t="n">
         <v>5</v>
@@ -15719,7 +15805,7 @@
         <v>39</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>5</v>
@@ -15733,7 +15819,7 @@
         <v>39</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F59" s="1" t="n">
         <v>5</v>
@@ -15747,7 +15833,7 @@
         <v>39</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F60" s="1" t="n">
         <v>4</v>
@@ -15761,7 +15847,7 @@
         <v>39</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>2</v>
@@ -15781,7 +15867,7 @@
         <v>42</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>10</v>
@@ -15806,7 +15892,7 @@
         <v>42</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F63" s="1" t="n">
         <v>10</v>
@@ -15820,7 +15906,7 @@
         <v>42</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F64" s="1" t="n">
         <v>10</v>
@@ -15834,7 +15920,7 @@
         <v>42</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F65" s="1" t="n">
         <v>9</v>
@@ -15848,7 +15934,7 @@
         <v>42</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F66" s="1" t="n">
         <v>8</v>
@@ -15862,7 +15948,7 @@
         <v>42</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F67" s="1" t="n">
         <v>4</v>
@@ -15876,7 +15962,7 @@
         <v>42</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F68" s="1" t="n">
         <v>3</v>
@@ -15890,7 +15976,7 @@
         <v>42</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F69" s="1" t="n">
         <v>1</v>
@@ -15910,7 +15996,7 @@
         <v>45</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F70" s="1" t="n">
         <v>8</v>
@@ -15935,7 +16021,7 @@
         <v>45</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F71" s="1" t="n">
         <v>7</v>
@@ -15949,7 +16035,7 @@
         <v>45</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F72" s="1" t="n">
         <v>7</v>
@@ -15963,7 +16049,7 @@
         <v>45</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F73" s="1" t="n">
         <v>6</v>
@@ -15977,7 +16063,7 @@
         <v>45</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F74" s="1" t="n">
         <v>6</v>
@@ -15991,7 +16077,7 @@
         <v>45</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F75" s="1" t="n">
         <v>6</v>
@@ -16005,7 +16091,7 @@
         <v>45</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F76" s="1" t="n">
         <v>5</v>
@@ -16019,7 +16105,7 @@
         <v>45</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F77" s="1" t="n">
         <v>5</v>
@@ -16033,7 +16119,7 @@
         <v>45</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F78" s="1" t="n">
         <v>4</v>
@@ -16047,7 +16133,7 @@
         <v>45</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F79" s="1" t="n">
         <v>4</v>
@@ -16061,7 +16147,7 @@
         <v>45</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F80" s="1" t="n">
         <v>4</v>
@@ -16075,7 +16161,7 @@
         <v>45</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F81" s="1" t="n">
         <v>3</v>
@@ -16089,7 +16175,7 @@
         <v>45</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F82" s="1" t="n">
         <v>3</v>
@@ -16099,7 +16185,7 @@
       <c r="A83" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B83" s="9" t="s">
+      <c r="B83" s="10" t="s">
         <v>50</v>
       </c>
       <c r="C83" s="1" t="s">
@@ -16109,7 +16195,7 @@
         <v>49</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F83" s="1" t="n">
         <v>8</v>
@@ -16134,7 +16220,7 @@
         <v>49</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F84" s="1" t="n">
         <v>7</v>
@@ -16148,7 +16234,7 @@
         <v>49</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F85" s="1" t="n">
         <v>7</v>
@@ -16162,7 +16248,7 @@
         <v>49</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F86" s="1" t="n">
         <v>7</v>
@@ -16176,7 +16262,7 @@
         <v>49</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F87" s="1" t="n">
         <v>5</v>
@@ -16190,7 +16276,7 @@
         <v>49</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F88" s="1" t="n">
         <v>5</v>
@@ -16204,7 +16290,7 @@
         <v>49</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F89" s="1" t="n">
         <v>3</v>
@@ -16224,7 +16310,7 @@
         <v>52</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F90" s="1" t="n">
         <v>7</v>
@@ -16237,7 +16323,7 @@
       <c r="A91" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B91" s="10" t="s">
+      <c r="B91" s="14" t="s">
         <v>56</v>
       </c>
       <c r="C91" s="1" t="s">
@@ -16247,7 +16333,7 @@
         <v>55</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F91" s="1" t="n">
         <v>8</v>
@@ -16272,7 +16358,7 @@
         <v>55</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F92" s="1" t="n">
         <v>6</v>
@@ -16286,7 +16372,7 @@
         <v>55</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F93" s="1" t="n">
         <v>6</v>
@@ -16300,7 +16386,7 @@
         <v>55</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F94" s="1" t="n">
         <v>5</v>
@@ -16314,7 +16400,7 @@
         <v>55</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F95" s="1" t="n">
         <v>5</v>
@@ -16334,7 +16420,7 @@
         <v>58</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F96" s="1" t="n">
         <v>6</v>
@@ -16359,7 +16445,7 @@
         <v>58</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F97" s="1" t="n">
         <v>6</v>
@@ -16373,7 +16459,7 @@
         <v>58</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F98" s="1" t="n">
         <v>6</v>
@@ -16387,7 +16473,7 @@
         <v>58</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F99" s="1" t="n">
         <v>5</v>
@@ -16401,7 +16487,7 @@
         <v>58</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F100" s="1" t="n">
         <v>5</v>
@@ -16415,7 +16501,7 @@
         <v>58</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F101" s="1" t="n">
         <v>4</v>
@@ -16429,7 +16515,7 @@
         <v>58</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F102" s="1" t="n">
         <v>4</v>
@@ -16439,7 +16525,7 @@
       <c r="A103" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B103" s="9" t="s">
+      <c r="B103" s="10" t="s">
         <v>62</v>
       </c>
       <c r="C103" s="1" t="s">
@@ -16449,7 +16535,7 @@
         <v>61</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F103" s="1" t="n">
         <v>8</v>
@@ -16472,7 +16558,7 @@
         <v>64</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F104" s="1" t="n">
         <v>10</v>
@@ -16497,7 +16583,7 @@
         <v>64</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F105" s="1" t="n">
         <v>6</v>
@@ -16511,7 +16597,7 @@
         <v>64</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F106" s="1" t="n">
         <v>5</v>
@@ -16525,7 +16611,7 @@
         <v>64</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F107" s="1" t="n">
         <v>4</v>
@@ -16539,7 +16625,7 @@
         <v>64</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F108" s="1" t="n">
         <v>4</v>
@@ -16553,7 +16639,7 @@
         <v>64</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F109" s="1" t="n">
         <v>4</v>
@@ -16573,7 +16659,7 @@
         <v>67</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F110" s="1" t="n">
         <v>10</v>
@@ -16598,7 +16684,7 @@
         <v>67</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F111" s="1" t="n">
         <v>10</v>
@@ -16612,7 +16698,7 @@
         <v>67</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F112" s="1" t="n">
         <v>9</v>
@@ -16626,7 +16712,7 @@
         <v>67</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F113" s="1" t="n">
         <v>6</v>
@@ -16640,7 +16726,7 @@
         <v>67</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F114" s="1" t="n">
         <v>1</v>
@@ -16660,7 +16746,7 @@
         <v>70</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F115" s="1" t="n">
         <v>9</v>
@@ -16685,7 +16771,7 @@
         <v>70</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F116" s="1" t="n">
         <v>7</v>
@@ -16699,7 +16785,7 @@
         <v>70</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F117" s="1" t="n">
         <v>6</v>
@@ -16713,7 +16799,7 @@
         <v>70</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F118" s="1" t="n">
         <v>5</v>
@@ -16727,7 +16813,7 @@
         <v>70</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="F119" s="1" t="n">
         <v>5</v>
@@ -16741,7 +16827,7 @@
         <v>70</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F120" s="1" t="n">
         <v>5</v>
@@ -16755,7 +16841,7 @@
         <v>70</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F121" s="1" t="n">
         <v>3</v>
@@ -16769,7 +16855,7 @@
         <v>70</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F122" s="1" t="n">
         <v>3</v>
@@ -16783,7 +16869,7 @@
         <v>70</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F123" s="1" t="n">
         <v>2</v>
@@ -16803,7 +16889,7 @@
         <v>73</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F124" s="1" t="n">
         <v>2</v>
@@ -16816,7 +16902,7 @@
       <c r="A125" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B125" s="10" t="s">
+      <c r="B125" s="14" t="s">
         <v>76</v>
       </c>
       <c r="C125" s="1" t="s">
@@ -16826,7 +16912,7 @@
         <v>24</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F125" s="1" t="n">
         <v>10</v>
@@ -16851,7 +16937,7 @@
         <v>24</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F126" s="1" t="n">
         <v>9</v>
@@ -16865,7 +16951,7 @@
         <v>24</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F127" s="1" t="n">
         <v>8</v>
@@ -16879,7 +16965,7 @@
         <v>24</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F128" s="1" t="n">
         <v>6</v>
@@ -16893,7 +16979,7 @@
         <v>24</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F129" s="1" t="n">
         <v>6</v>
@@ -16907,7 +16993,7 @@
         <v>24</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F130" s="1" t="n">
         <v>4</v>
@@ -16921,7 +17007,7 @@
         <v>24</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F131" s="1" t="n">
         <v>2</v>
@@ -16935,7 +17021,7 @@
         <v>24</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F132" s="1" t="n">
         <v>1</v>
